--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487486_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487486_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0827</v>
+        <v>2.2612</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9167</v>
+        <v>0.405</v>
       </c>
       <c r="F2" t="n">
-        <v>3.166</v>
+        <v>1.8562</v>
       </c>
       <c r="G2" t="n">
         <v>0.0858</v>
@@ -610,13 +610,13 @@
         <v>1.3709</v>
       </c>
       <c r="S2" t="n">
-        <v>2.975</v>
+        <v>1.1535</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3899</v>
+        <v>-0.1218</v>
       </c>
       <c r="U2" t="n">
-        <v>2.585</v>
+        <v>1.2752</v>
       </c>
       <c r="V2" t="n">
         <v>0.8260999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2547</v>
+        <v>1.9046</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9989</v>
+        <v>1.4082</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2558</v>
+        <v>0.4964</v>
       </c>
       <c r="G3" t="n">
         <v>1.2017</v>
@@ -688,13 +688,13 @@
         <v>1.7626</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2972</v>
+        <v>0.3527</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5123</v>
+        <v>-0.1029</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2151</v>
+        <v>0.4557</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2166</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. PEREZ MARTIN</t>
+          <t>M. GONZALEZ BLAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7181</v>
+        <v>0.8817</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7074</v>
+        <v>0.1153</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0107</v>
+        <v>0.7664</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.6535</v>
+        <v>1.6193</v>
       </c>
       <c r="H4" t="n">
-        <v>0.246</v>
+        <v>1.8973</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.8995</v>
+        <v>-0.2781</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1816</v>
+        <v>2.6683</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3793</v>
+        <v>1.4818</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5610000000000001</v>
+        <v>1.1865</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4718</v>
+        <v>-1.049</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1333</v>
+        <v>0.4156</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3385</v>
+        <v>-1.4646</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5668</v>
+        <v>0.3917</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.1543</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5668</v>
+        <v>2.546</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1364</v>
+        <v>-0.5209</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3276</v>
+        <v>-0.674</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1911</v>
+        <v>0.1531</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9412</v>
+        <v>-0.6083</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2166</v>
+        <v>0.2754</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2754</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. CABAÑEROS MORALA</t>
+          <t>R. PEREZ MARTIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6609</v>
+        <v>0.5531</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8157</v>
+        <v>0.8097</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1548</v>
+        <v>-0.2566</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1527</v>
+        <v>-1.6535</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7285</v>
+        <v>0.246</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5758</v>
+        <v>-1.8995</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0912</v>
+        <v>-0.1816</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6618000000000001</v>
+        <v>0.3793</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5706</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0615</v>
+        <v>-1.4718</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0667</v>
+        <v>-0.1333</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0052</v>
+        <v>-1.3385</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5875</v>
+        <v>1.5668</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5875</v>
+        <v>1.5668</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7766999999999999</v>
+        <v>-0.3014</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9069</v>
+        <v>-0.2253</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1302</v>
+        <v>-0.0762</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5507</v>
+        <v>0.9412</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5507</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4923</v>
+        <v>0.3816</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8898</v>
+        <v>-2.4014</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3821</v>
+        <v>2.7831</v>
       </c>
       <c r="G6" t="n">
         <v>-4.0709</v>
@@ -922,13 +922,13 @@
         <v>2.7419</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2302</v>
+        <v>0.1195</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6146</v>
+        <v>0.1029</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3843</v>
+        <v>0.0166</v>
       </c>
       <c r="V6" t="n">
         <v>2.7662</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. GONZALEZ BLAS</t>
+          <t>P. CABAÑEROS MORALA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2356</v>
+        <v>0.1225</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6011</v>
+        <v>0.304</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3655</v>
+        <v>-0.1815</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6193</v>
+        <v>-0.1527</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8973</v>
+        <v>-0.7285</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2781</v>
+        <v>0.5758</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6683</v>
+        <v>-0.0912</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4818</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1865</v>
+        <v>0.5706</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.049</v>
+        <v>-0.0615</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4156</v>
+        <v>-0.0667</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4646</v>
+        <v>0.0052</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3917</v>
+        <v>0.5875</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1543</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.546</v>
+        <v>0.5875</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6383</v>
+        <v>0.2383</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.3904</v>
+        <v>0.3952</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2479</v>
+        <v>-0.1569</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6083</v>
+        <v>-0.5507</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8837</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="8">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3674</v>
+        <v>-0.2651</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.224</v>
+        <v>-1.1216</v>
       </c>
       <c r="F8" t="n">
         <v>0.8565</v>
@@ -1078,10 +1078,10 @@
         <v>1.3709</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4093</v>
+        <v>-0.307</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.297</v>
+        <v>-0.1947</v>
       </c>
       <c r="U8" t="n">
         <v>-0.1123</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5317</v>
+        <v>-1.3225</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.375</v>
+        <v>-0.2726</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1567</v>
+        <v>-1.0498</v>
       </c>
       <c r="G9" t="n">
         <v>0.0471</v>
@@ -1156,13 +1156,13 @@
         <v>0.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7539</v>
+        <v>-0.5446</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4158</v>
+        <v>-0.3135</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3381</v>
+        <v>-0.2311</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2166</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0329</v>
+        <v>-2.1306</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3073</v>
+        <v>-2.5119</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2744</v>
+        <v>0.3813</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5273</v>
@@ -1234,13 +1234,13 @@
         <v>1.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1419</v>
+        <v>0.0441</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4317</v>
+        <v>0.227</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2898</v>
+        <v>-0.1829</v>
       </c>
       <c r="V10" t="n">
         <v>1.3318</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3392</v>
+        <v>-2.6847</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.4684</v>
+        <v>-5.1614</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1292</v>
+        <v>2.4767</v>
       </c>
       <c r="G11" t="n">
         <v>-5.0688</v>
@@ -1312,13 +1312,13 @@
         <v>2.1543</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6241</v>
+        <v>0.0304</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4529</v>
+        <v>-0.1459</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1712</v>
+        <v>0.1763</v>
       </c>
       <c r="V11" t="n">
         <v>2.1578</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2981000000000003</v>
+        <v>-0.2981999999999996</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.4269</v>
+        <v>-8.4267</v>
       </c>
       <c r="F12" t="n">
-        <v>8.1287</v>
+        <v>8.128700000000002</v>
       </c>
       <c r="G12" t="n">
         <v>-10.8691</v>
@@ -1363,7 +1363,7 @@
         <v>-15.6396</v>
       </c>
       <c r="J12" t="n">
-        <v>-5.316700000000001</v>
+        <v>-5.3167</v>
       </c>
       <c r="K12" t="n">
         <v>3.0259</v>
@@ -1378,7 +1378,7 @@
         <v>1.7445</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.296900000000001</v>
+        <v>-7.296899999999999</v>
       </c>
       <c r="P12" t="n">
         <v>5.8754</v>
@@ -1390,19 +1390,19 @@
         <v>15.6677</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2645999999999999</v>
+        <v>0.2646000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0529</v>
+        <v>-1.053</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3174</v>
+        <v>1.3175</v>
       </c>
       <c r="V12" t="n">
         <v>4.4309</v>
       </c>
       <c r="W12" t="n">
-        <v>7.735199999999999</v>
+        <v>7.7352</v>
       </c>
       <c r="X12" t="n">
         <v>-3.304399999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.493</v>
+        <v>5.1172</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5133</v>
+        <v>3.025</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9797</v>
+        <v>2.0922</v>
       </c>
       <c r="G13" t="n">
         <v>5.9552</v>
@@ -1468,13 +1468,13 @@
         <v>1.3709</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9127</v>
+        <v>-0.2885</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.5445</v>
+        <v>-1.0328</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6318</v>
+        <v>0.7443</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9412</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. NJIE</t>
+          <t>J. PRIETO LORIENTE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4137</v>
+        <v>2.6228</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5348</v>
+        <v>-0.1071</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8788</v>
+        <v>2.7299</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6322</v>
+        <v>4.1808</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.591</v>
+        <v>-0.5029</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2232</v>
+        <v>4.6837</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1323</v>
+        <v>3.1976</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2535</v>
+        <v>0.0356</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1212</v>
+        <v>3.162</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7645</v>
+        <v>0.9832</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3375</v>
+        <v>-0.5385</v>
       </c>
       <c r="O14" t="n">
-        <v>1.102</v>
+        <v>1.5217</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1958</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1751</v>
+        <v>-2.1543</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9792</v>
+        <v>1.5668</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3678</v>
+        <v>-0.5799</v>
       </c>
       <c r="T14" t="n">
-        <v>2.0161</v>
+        <v>-0.7599</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3517</v>
+        <v>0.18</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3905</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8260999999999999</v>
+        <v>-0.3905</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. PRIETO LORIENTE</t>
+          <t>C. FERNANDEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0338</v>
+        <v>1.4851</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2094</v>
+        <v>1.5979</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2432</v>
+        <v>-0.1128</v>
       </c>
       <c r="G15" t="n">
-        <v>4.1808</v>
+        <v>1.5462</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5029</v>
+        <v>0.1364</v>
       </c>
       <c r="I15" t="n">
-        <v>4.6837</v>
+        <v>1.4097</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1976</v>
+        <v>1.5264</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0356</v>
+        <v>0.951</v>
       </c>
       <c r="L15" t="n">
-        <v>3.162</v>
+        <v>0.5755</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9832</v>
+        <v>0.0197</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5385</v>
+        <v>-0.8145</v>
       </c>
       <c r="O15" t="n">
-        <v>1.5217</v>
+        <v>0.8343</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.5875</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1543</v>
+        <v>-0.9792</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5668</v>
+        <v>0.9792</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.169</v>
+        <v>-0.061</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8622</v>
+        <v>-0.1659</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3068</v>
+        <v>0.1048</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3905</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3905</v>
+        <v>1.2166</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. FERNANDEZ ALVAREZ</t>
+          <t>G. RODRIGUEZ LUQUE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9523</v>
+        <v>0.9777</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4956</v>
+        <v>-0.7423999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5433</v>
+        <v>1.72</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5462</v>
+        <v>1.647</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1364</v>
+        <v>1.0712</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4097</v>
+        <v>0.5758</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5264</v>
+        <v>0.9585</v>
       </c>
       <c r="K16" t="n">
-        <v>0.951</v>
+        <v>0.3879</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5755</v>
+        <v>0.5706</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0197</v>
+        <v>0.6885</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8145</v>
+        <v>0.6833</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8343</v>
+        <v>0.0052</v>
       </c>
       <c r="P16" t="n">
+        <v>-1.7626</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-1.9585</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.1958</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.2576</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.1698</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.6659</v>
+      </c>
+      <c r="W16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-0.9792</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.9792</v>
-      </c>
-      <c r="S16" t="n">
-        <v>-0.5938</v>
-      </c>
-      <c r="T16" t="n">
-        <v>-0.2682</v>
-      </c>
-      <c r="U16" t="n">
-        <v>-0.3256</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.2166</v>
-      </c>
       <c r="X16" t="n">
-        <v>-1.2166</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ LUQUE</t>
+          <t>P. NJIE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2779</v>
+        <v>0.7478</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3564</v>
+        <v>-0.0002</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6343</v>
+        <v>0.748</v>
       </c>
       <c r="G17" t="n">
-        <v>1.647</v>
+        <v>0.6322</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0712</v>
+        <v>-0.591</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5758</v>
+        <v>1.2232</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9585</v>
+        <v>-0.1323</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3879</v>
+        <v>-0.2535</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5706</v>
+        <v>0.1212</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6885</v>
+        <v>0.7645</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6833</v>
+        <v>-0.3375</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0052</v>
+        <v>1.102</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.7626</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9585</v>
+        <v>-1.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1958</v>
+        <v>0.9792</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2724</v>
+        <v>0.7019</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3564</v>
+        <v>0.4811</v>
       </c>
       <c r="U17" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.2209</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6659</v>
+        <v>-0.3905</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6659</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. LUCENTE</t>
+          <t>A. PACHECO MARTINEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6459</v>
+        <v>-0.5391</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6302</v>
+        <v>-3.7873</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9843</v>
+        <v>3.2481</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5131</v>
+        <v>0.1254</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2818</v>
+        <v>-1.9361</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7685999999999999</v>
+        <v>2.0615</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-1.6577</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0141</v>
+        <v>-1.6674</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2021</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2989</v>
+        <v>1.7832</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2677</v>
+        <v>-0.2687</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5666</v>
+        <v>2.0519</v>
       </c>
       <c r="P18" t="n">
+        <v>-0.5875</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-1.9585</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-2.9377</v>
-      </c>
       <c r="R18" t="n">
-        <v>0.9792</v>
+        <v>1.3709</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2174</v>
+        <v>-0.077</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2358</v>
+        <v>-0.4464</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9815</v>
+        <v>0.3694</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6083</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8837</v>
+        <v>0.2754</v>
       </c>
       <c r="X18" t="n">
         <v>-0.2754</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. PACHECO MARTINEZ</t>
+          <t>D. REIRIZ MENDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6756</v>
+        <v>-0.7104</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.7873</v>
+        <v>-0.092</v>
       </c>
       <c r="F19" t="n">
-        <v>3.1117</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1254</v>
+        <v>0.5162</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.9361</v>
+        <v>-0.2977</v>
       </c>
       <c r="I19" t="n">
-        <v>2.0615</v>
+        <v>0.8139</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.6577</v>
+        <v>0.1621</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.6674</v>
+        <v>0.0408</v>
       </c>
       <c r="L19" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.1212</v>
       </c>
       <c r="M19" t="n">
-        <v>1.7832</v>
+        <v>0.3541</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2687</v>
+        <v>-0.3385</v>
       </c>
       <c r="O19" t="n">
-        <v>2.0519</v>
+        <v>0.6926</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5875</v>
+        <v>0.5875</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3709</v>
+        <v>0.5875</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2135</v>
+        <v>-0.5975</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4464</v>
+        <v>-0.2541</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2329</v>
+        <v>-0.3435</v>
       </c>
       <c r="V19" t="n">
+        <v>-1.2166</v>
+      </c>
+      <c r="W19" t="n">
         <v>0</v>
       </c>
-      <c r="W19" t="n">
-        <v>0.2754</v>
-      </c>
       <c r="X19" t="n">
-        <v>-0.2754</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. REIRIZ MENDEZ</t>
+          <t>I. LUCENTE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0561</v>
+        <v>-1.1345</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1943</v>
+        <v>-2.9373</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8618</v>
+        <v>1.8028</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5162</v>
+        <v>-0.5131</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2977</v>
+        <v>-1.2818</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8139</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1621</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0408</v>
+        <v>-1.0141</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1212</v>
+        <v>0.2021</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3541</v>
+        <v>0.2989</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3385</v>
+        <v>-0.2677</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6926</v>
+        <v>0.5666</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5875</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5875</v>
+        <v>0.9792</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9433</v>
+        <v>0.7288</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3564</v>
+        <v>-0.0712</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5868</v>
+        <v>0.8</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2166</v>
+        <v>0.6083</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.8837</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9694</v>
+        <v>-1.6634</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3573</v>
+        <v>-1.562</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6121</v>
+        <v>-0.1014</v>
       </c>
       <c r="G21" t="n">
         <v>-1.5986</v>
@@ -2092,13 +2092,13 @@
         <v>0.5875</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7294</v>
+        <v>1.0354</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.3876</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1372</v>
+        <v>0.6478</v>
       </c>
       <c r="V21" t="n">
         <v>-1.492</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0649</v>
+        <v>-1.8603</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0359</v>
+        <v>-0.8312</v>
       </c>
       <c r="F22" t="n">
         <v>-1.0291</v>
@@ -2170,10 +2170,10 @@
         <v>0.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1782</v>
+        <v>0.0265</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1782</v>
+        <v>0.0265</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4605</v>
+        <v>-2.698</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1016</v>
+        <v>-2.6923</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3589</v>
+        <v>-0.0058</v>
       </c>
       <c r="G23" t="n">
         <v>-0.7562</v>
@@ -2248,13 +2248,13 @@
         <v>0.7834</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2965</v>
+        <v>0.466</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1494</v>
+        <v>0.26</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1471</v>
+        <v>0.206</v>
       </c>
       <c r="V23" t="n">
         <v>-0.0576</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2983000000000002</v>
+        <v>2.3449</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.1287</v>
+        <v>-8.1289</v>
       </c>
       <c r="F24" t="n">
-        <v>8.4268</v>
+        <v>10.4735</v>
       </c>
       <c r="G24" t="n">
         <v>10.8691</v>
@@ -2299,7 +2299,7 @@
         <v>15.6395</v>
       </c>
       <c r="J24" t="n">
-        <v>5.5523</v>
+        <v>5.552299999999998</v>
       </c>
       <c r="K24" t="n">
         <v>-1.7447</v>
@@ -2308,7 +2308,7 @@
         <v>7.297000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>5.316799999999999</v>
+        <v>5.3168</v>
       </c>
       <c r="N24" t="n">
         <v>-3.0258</v>
@@ -2323,16 +2323,16 @@
         <v>-15.6677</v>
       </c>
       <c r="R24" t="n">
-        <v>9.7921</v>
+        <v>9.792100000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2648</v>
+        <v>1.7821</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3176</v>
+        <v>-1.3175</v>
       </c>
       <c r="U24" t="n">
-        <v>1.0528</v>
+        <v>3.0995</v>
       </c>
       <c r="V24" t="n">
         <v>-4.4308</v>
